--- a/fot-app/public/forms/bypass-sheet-itr.xlsx
+++ b/fot-app/public/forms/bypass-sheet-itr.xlsx
@@ -30,7 +30,7 @@
     <t>АХО</t>
   </si>
   <si>
-    <t>Булгаков М.А.</t>
+    <t>Булгаков М.А., Муратов М.Х.</t>
   </si>
   <si>
     <t>ИТ</t>
@@ -633,11 +633,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.375" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
   </cols>
   <sheetData>
@@ -817,7 +820,7 @@
     <mergeCell ref="A5:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.17" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
       <mx:PLV Mode="0" OnePage="0" WScale="0"/>
